--- a/2.Cloning/CRISPR_KO/results/Tnfrsf12a/Tnfrsf12a-sgrna-designs.xlsx
+++ b/2.Cloning/CRISPR_KO/results/Tnfrsf12a/Tnfrsf12a-sgrna-designs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/HOME/Github/WetLab/2.Cloning/CRISPR_KO/results/Tnfrsf12a/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A48162D4-A5FD-AA45-BF5B-3E43AF6A2467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40859E15-713E-0046-B8C1-5595DEA44396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11980" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{3BE93FDC-99D8-3E4C-ADAA-75D846F931AC}"/>
+    <workbookView xWindow="-28940" yWindow="3380" windowWidth="27640" windowHeight="16940" xr2:uid="{3BE93FDC-99D8-3E4C-ADAA-75D846F931AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Tnfrsf12a-sgrna-designs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="91">
   <si>
     <t>Input</t>
   </si>
@@ -284,6 +284,15 @@
   </si>
   <si>
     <t>AAACACTTCAGGCTACTGTGGCCCC</t>
+  </si>
+  <si>
+    <t>sanger seq</t>
+  </si>
+  <si>
+    <t>accg</t>
+  </si>
+  <si>
+    <t>gttt</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66ECC393-7040-534B-BEC3-2ED8A597A0F5}">
-  <dimension ref="A1:AI18"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.2">
@@ -2148,6 +2157,20 @@
         <v>87</v>
       </c>
     </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2.Cloning/CRISPR_KO/results/Tnfrsf12a/Tnfrsf12a-sgrna-designs.xlsx
+++ b/2.Cloning/CRISPR_KO/results/Tnfrsf12a/Tnfrsf12a-sgrna-designs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/HOME/Github/WetLab/2.Cloning/CRISPR_KO/results/Tnfrsf12a/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40859E15-713E-0046-B8C1-5595DEA44396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C830EEC-F581-EA4C-999B-69AA4FDB93A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28940" yWindow="3380" windowWidth="27640" windowHeight="16940" xr2:uid="{3BE93FDC-99D8-3E4C-ADAA-75D846F931AC}"/>
   </bookViews>
@@ -289,10 +289,10 @@
     <t>sanger seq</t>
   </si>
   <si>
-    <t>accg</t>
-  </si>
-  <si>
     <t>gttt</t>
+  </si>
+  <si>
+    <t>caccg</t>
   </si>
 </sst>
 </file>
@@ -2162,13 +2162,13 @@
         <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
         <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
